--- a/excel_data/Super Veo3 Pro - Văn Thế Web V3_1677623071909745989.xlsx
+++ b/excel_data/Super Veo3 Pro - Văn Thế Web V3_1677623071909745989.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-16T09:41:21.265916</t>
+          <t>2026-04-16T10:13:54.868744</t>
         </is>
       </c>
     </row>

--- a/excel_data/Super Veo3 Pro - Văn Thế Web V3_1677623071909745989.xlsx
+++ b/excel_data/Super Veo3 Pro - Văn Thế Web V3_1677623071909745989.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Tổng: 834</t>
+          <t>Tổng: None</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-04-16T10:13:54.868744</t>
+          <t>2026-04-17T15:24:14.310274</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,11 @@
       </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -849,7 +853,11 @@
       </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="2" t="n">
@@ -936,7 +944,11 @@
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="2" t="n">
@@ -965,7 +977,11 @@
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -994,7 +1010,11 @@
       </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="2" t="n">
@@ -1023,7 +1043,11 @@
       </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="2" t="n">
@@ -1139,7 +1163,11 @@
       </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="2" t="n">
@@ -1168,7 +1196,11 @@
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="2" t="n">
@@ -1197,7 +1229,11 @@
       </c>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="45" customHeight="1">
       <c r="A28" s="2" t="n">
@@ -1255,7 +1291,11 @@
       </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="2" t="n">
@@ -1284,7 +1324,11 @@
       </c>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="45" customHeight="1">
       <c r="A31" s="2" t="n">
@@ -1342,7 +1386,11 @@
       </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="45" customHeight="1">
       <c r="A33" s="2" t="n">
@@ -1400,7 +1448,11 @@
       </c>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="2" t="n">
@@ -1487,7 +1539,11 @@
       </c>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="45" customHeight="1">
       <c r="A38" s="2" t="n">
@@ -1516,7 +1572,11 @@
       </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
-      <c r="I38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="45" customHeight="1">
       <c r="A39" s="2" t="n">
@@ -1545,7 +1605,11 @@
       </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="2" t="n">
@@ -1574,7 +1638,11 @@
       </c>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="45" customHeight="1">
       <c r="A41" s="2" t="n">
@@ -1603,7 +1671,11 @@
       </c>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="45" customHeight="1">
       <c r="A42" s="2" t="n">
@@ -1632,7 +1704,11 @@
       </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="45" customHeight="1">
       <c r="A43" s="2" t="n">
@@ -1661,7 +1737,11 @@
       </c>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="45" customHeight="1">
       <c r="A44" s="2" t="n">
@@ -1690,7 +1770,11 @@
       </c>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="45" customHeight="1">
       <c r="A45" s="2" t="n">
@@ -1719,7 +1803,11 @@
       </c>
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="45" customHeight="1">
       <c r="A46" s="2" t="n">
@@ -1748,7 +1836,11 @@
       </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="45" customHeight="1">
       <c r="A47" s="2" t="n">
@@ -1806,7 +1898,11 @@
       </c>
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="45" customHeight="1">
       <c r="A49" s="2" t="n">
@@ -4240,9 +4336,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H132" s="2" t="inlineStr"/>
-      <c r="I132" s="2" t="inlineStr"/>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="45" customHeight="1">
       <c r="A133" s="2" t="n">
@@ -4269,9 +4373,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H133" s="2" t="inlineStr"/>
-      <c r="I133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="45" customHeight="1">
       <c r="A134" s="2" t="n">
@@ -4298,9 +4410,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H134" s="2" t="inlineStr"/>
-      <c r="I134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="45" customHeight="1">
       <c r="A135" s="2" t="n">
@@ -4327,9 +4447,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H135" s="2" t="inlineStr"/>
-      <c r="I135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="45" customHeight="1">
       <c r="A136" s="2" t="n">
@@ -4356,9 +4484,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H136" s="2" t="inlineStr"/>
-      <c r="I136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="45" customHeight="1">
       <c r="A137" s="2" t="n">
@@ -4385,9 +4521,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H137" s="2" t="inlineStr"/>
-      <c r="I137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="45" customHeight="1">
       <c r="A138" s="2" t="n">
@@ -4414,9 +4558,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H138" s="2" t="inlineStr"/>
-      <c r="I138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="45" customHeight="1">
       <c r="A139" s="2" t="n">
@@ -4443,9 +4595,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H139" s="2" t="inlineStr"/>
-      <c r="I139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="45" customHeight="1">
       <c r="A140" s="2" t="n">
@@ -4472,9 +4632,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H140" s="2" t="inlineStr"/>
-      <c r="I140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="45" customHeight="1">
       <c r="A141" s="2" t="n">
@@ -4501,9 +4669,17 @@
           <t>Thành viên</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
       <c r="H141" s="2" t="inlineStr"/>
-      <c r="I141" s="2" t="inlineStr"/>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="45" customHeight="1">
       <c r="A142" s="2" t="n">
